--- a/sheets/대금율보/검수/미워도 다시한번.xlsx
+++ b/sheets/대금율보/검수/미워도 다시한번.xlsx
@@ -3573,19 +3573,11 @@
       <c r="C5" s="25"/>
       <c r="D5" s="23"/>
       <c r="E5" s="25"/>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F5" s="23"/>
       <c r="G5" s="25"/>
       <c r="H5" s="23"/>
       <c r="I5" s="25"/>
-      <c r="J5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="23"/>
       <c r="K5" s="25"/>
       <c r="L5" s="23" t="inlineStr">
         <is>
@@ -3735,35 +3727,19 @@
         </is>
       </c>
       <c r="C9" s="25"/>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D9" s="23"/>
       <c r="E9" s="25"/>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F9" s="23"/>
       <c r="G9" s="25"/>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H9" s="23"/>
       <c r="I9" s="25"/>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">南‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K9" s="25"/>
-      <c r="L9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L9" s="23"/>
       <c r="M9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
@@ -3894,11 +3870,7 @@
       <c r="C13" s="25"/>
       <c r="D13" s="23"/>
       <c r="E13" s="25"/>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F13" s="23"/>
       <c r="G13" s="25"/>
       <c r="H13" s="23"/>
       <c r="I13" s="25"/>
@@ -4044,31 +4016,15 @@
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="25"/>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D17" s="23"/>
       <c r="E17" s="25"/>
       <c r="F17" s="23"/>
       <c r="G17" s="25"/>
-      <c r="H17" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H17" s="23"/>
       <c r="I17" s="25"/>
-      <c r="J17" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J17" s="23"/>
       <c r="K17" s="25"/>
-      <c r="L17" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L17" s="23"/>
       <c r="M17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
@@ -4210,19 +4166,11 @@
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F21" s="23"/>
       <c r="G21" s="25"/>
       <c r="H21" s="23"/>
       <c r="I21" s="25"/>
-      <c r="J21" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J21" s="23"/>
       <c r="K21" s="25"/>
       <c r="L21" s="23" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/미워도 다시한번.xlsx
+++ b/sheets/대금율보/검수/미워도 다시한번.xlsx
@@ -3461,24 +3461,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.84" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.84" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23"/>
       <c r="C4" s="25"/>
@@ -3567,7 +3567,7 @@
       <c r="L4" s="23"/>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.84" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23"/>
       <c r="C5" s="25"/>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="M5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.84" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="M6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.84" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="M7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.84" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
       <c r="C8" s="25"/>
@@ -3719,7 +3719,7 @@
       <c r="L8" s="23"/>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.84" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
       <c r="L9" s="23"/>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.84" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="M10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.84" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.84" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
       <c r="C12" s="25"/>
@@ -3864,7 +3864,7 @@
       <c r="L12" s="23"/>
       <c r="M12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.84" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
       <c r="C13" s="25"/>
@@ -3884,7 +3884,7 @@
       <c r="L13" s="23"/>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.84" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="M14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.84" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="M15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.84" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
       <c r="C16" s="25"/>
@@ -4012,7 +4012,7 @@
       <c r="L16" s="23"/>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.84" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="25"/>
@@ -4027,7 +4027,7 @@
       <c r="L17" s="23"/>
       <c r="M17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.84" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
       <c r="C18" s="27"/>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="M18" s="27"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.84" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="23"/>
       <c r="C19" s="24"/>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.84" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="23"/>
       <c r="C20" s="25"/>
@@ -4152,7 +4152,7 @@
       <c r="L20" s="23"/>
       <c r="M20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.84" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="23"/>
       <c r="C21" s="25"/>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="M21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.84" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="23"/>
       <c r="C22" s="27"/>
@@ -4234,6 +4234,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>